--- a/services/data_raw/eurostat/AT_cars_road_eqs_carpda.xlsx
+++ b/services/data_raw/eurostat/AT_cars_road_eqs_carpda.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,89 +417,89 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>freq</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>mot_nrg</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>geo\TIME_PERIOD</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2013</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2014</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -572,7 +560,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -587,7 +575,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Petroleum products [PET]</t>
+          <t>Petrol [PET]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -633,7 +621,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -694,7 +682,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -755,7 +743,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -816,7 +804,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -877,7 +865,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -938,7 +926,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -999,7 +987,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1060,7 +1048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1121,7 +1109,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1182,7 +1170,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1243,7 +1231,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1304,7 +1292,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1365,7 +1353,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1410,7 +1398,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1455,7 +1443,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1516,7 +1504,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">

--- a/services/data_raw/eurostat/AT_cars_road_eqs_carpda.xlsx
+++ b/services/data_raw/eurostat/AT_cars_road_eqs_carpda.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Liquefied petroleum gases (LPG) [LPG]</t>
+          <t>Petrol (excluding hybrids) [PET_X_HYB]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -645,40 +645,40 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>2003699</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2011104</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2019139</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2038019</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2080434</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>2139239</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>2179235</v>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>2195578</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>2197006</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>2194125</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2188368</v>
       </c>
       <c r="Q4" t="n">
-        <v>2172</v>
+        <v>2186500</v>
       </c>
     </row>
     <row r="5">
@@ -697,7 +697,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Diesel [DIE]</t>
+          <t>Hybrid electric-petrol [ELC_PET_HYB]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -706,40 +706,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2621588</v>
+        <v>9664</v>
       </c>
       <c r="G5" t="n">
-        <v>2663654</v>
+        <v>11505</v>
       </c>
       <c r="H5" t="n">
-        <v>2703999</v>
+        <v>13327</v>
       </c>
       <c r="I5" t="n">
-        <v>2750383</v>
+        <v>16531</v>
       </c>
       <c r="J5" t="n">
-        <v>2771925</v>
+        <v>22290</v>
       </c>
       <c r="K5" t="n">
-        <v>2778795</v>
+        <v>28619</v>
       </c>
       <c r="L5" t="n">
-        <v>2779026</v>
+        <v>37897</v>
       </c>
       <c r="M5" t="n">
-        <v>2776651</v>
+        <v>54472</v>
       </c>
       <c r="N5" t="n">
-        <v>2745471</v>
+        <v>81745</v>
       </c>
       <c r="O5" t="n">
-        <v>2692682</v>
+        <v>109361</v>
       </c>
       <c r="P5" t="n">
-        <v>2640528</v>
+        <v>141980</v>
       </c>
       <c r="Q5" t="n">
-        <v>2582446</v>
+        <v>188324</v>
       </c>
     </row>
     <row r="6">
@@ -758,7 +758,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Natural gas [GAS]</t>
+          <t>Plug-in hybrid petrol-electric [ELC_PET_PI]</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -767,40 +767,40 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2219</v>
+        <v>385</v>
       </c>
       <c r="G6" t="n">
-        <v>2397</v>
+        <v>727</v>
       </c>
       <c r="H6" t="n">
-        <v>2475</v>
+        <v>1458</v>
       </c>
       <c r="I6" t="n">
-        <v>2457</v>
+        <v>2165</v>
       </c>
       <c r="J6" t="n">
-        <v>2433</v>
+        <v>3749</v>
       </c>
       <c r="K6" t="n">
-        <v>2365</v>
+        <v>5467</v>
       </c>
       <c r="L6" t="n">
-        <v>2602</v>
+        <v>7748</v>
       </c>
       <c r="M6" t="n">
-        <v>2753</v>
+        <v>14511</v>
       </c>
       <c r="N6" t="n">
-        <v>2654</v>
+        <v>27233</v>
       </c>
       <c r="O6" t="n">
-        <v>2564</v>
+        <v>38923</v>
       </c>
       <c r="P6" t="n">
-        <v>2342</v>
+        <v>53459</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>69264</v>
       </c>
     </row>
     <row r="7">
@@ -819,7 +819,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Electricity [ELC]</t>
+          <t>Diesel [DIE]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -828,40 +828,40 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2070</v>
+        <v>2621588</v>
       </c>
       <c r="G7" t="n">
-        <v>3386</v>
+        <v>2663654</v>
       </c>
       <c r="H7" t="n">
-        <v>5032</v>
+        <v>2703999</v>
       </c>
       <c r="I7" t="n">
-        <v>9073</v>
+        <v>2750383</v>
       </c>
       <c r="J7" t="n">
-        <v>14618</v>
+        <v>2771925</v>
       </c>
       <c r="K7" t="n">
-        <v>20831</v>
+        <v>2778795</v>
       </c>
       <c r="L7" t="n">
-        <v>29523</v>
+        <v>2779026</v>
       </c>
       <c r="M7" t="n">
-        <v>44507</v>
+        <v>2776651</v>
       </c>
       <c r="N7" t="n">
-        <v>76539</v>
+        <v>2745471</v>
       </c>
       <c r="O7" t="n">
-        <v>110225</v>
+        <v>2692682</v>
       </c>
       <c r="P7" t="n">
-        <v>155490</v>
+        <v>2640528</v>
       </c>
       <c r="Q7" t="n">
-        <v>200603</v>
+        <v>2582446</v>
       </c>
     </row>
     <row r="8">
@@ -880,7 +880,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alternative energy [ALT]</t>
+          <t>Diesel (excluding hybrids) [DIE_X_HYB]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -889,40 +889,40 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5972</v>
+        <v>2621133</v>
       </c>
       <c r="G8" t="n">
-        <v>7931</v>
+        <v>2663063</v>
       </c>
       <c r="H8" t="n">
-        <v>10125</v>
+        <v>2702922</v>
       </c>
       <c r="I8" t="n">
-        <v>14459</v>
+        <v>2749046</v>
       </c>
       <c r="J8" t="n">
-        <v>20180</v>
+        <v>2770470</v>
       </c>
       <c r="K8" t="n">
-        <v>26732</v>
+        <v>2776332</v>
       </c>
       <c r="L8" t="n">
-        <v>35642</v>
+        <v>2772854</v>
       </c>
       <c r="M8" t="n">
-        <v>50615</v>
+        <v>2762273</v>
       </c>
       <c r="N8" t="n">
-        <v>82381</v>
+        <v>2717475</v>
       </c>
       <c r="O8" t="n">
-        <v>115799</v>
+        <v>2651280</v>
       </c>
       <c r="P8" t="n">
-        <v>160671</v>
+        <v>2584985</v>
       </c>
       <c r="Q8" t="n">
-        <v>205359</v>
+        <v>2510099</v>
       </c>
     </row>
     <row r="9">
@@ -941,7 +941,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Petrol (excluding hybrids) [PET_X_HYB]</t>
+          <t>Hybrid diesel-electric [ELC_DIE_HYB]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -950,40 +950,40 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2003699</v>
+        <v>432</v>
       </c>
       <c r="G9" t="n">
-        <v>2011104</v>
+        <v>542</v>
       </c>
       <c r="H9" t="n">
-        <v>2019139</v>
+        <v>1028</v>
       </c>
       <c r="I9" t="n">
-        <v>2038019</v>
+        <v>1224</v>
       </c>
       <c r="J9" t="n">
-        <v>2080434</v>
+        <v>1268</v>
       </c>
       <c r="K9" t="n">
-        <v>2139239</v>
+        <v>2220</v>
       </c>
       <c r="L9" t="n">
-        <v>2179235</v>
+        <v>5878</v>
       </c>
       <c r="M9" t="n">
-        <v>2195578</v>
+        <v>13652</v>
       </c>
       <c r="N9" t="n">
-        <v>2197006</v>
+        <v>26208</v>
       </c>
       <c r="O9" t="n">
-        <v>2194125</v>
+        <v>38745</v>
       </c>
       <c r="P9" t="n">
-        <v>2188368</v>
+        <v>52138</v>
       </c>
       <c r="Q9" t="n">
-        <v>2186500</v>
+        <v>66843</v>
       </c>
     </row>
     <row r="10">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hybrid electric-petrol [ELC_PET_HYB]</t>
+          <t>Plug-in hybrid diesel-electric [ELC_DIE_PI]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1011,40 +1011,40 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9664</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>11505</v>
+        <v>49</v>
       </c>
       <c r="H10" t="n">
-        <v>13327</v>
+        <v>49</v>
       </c>
       <c r="I10" t="n">
-        <v>16531</v>
+        <v>113</v>
       </c>
       <c r="J10" t="n">
-        <v>22290</v>
+        <v>187</v>
       </c>
       <c r="K10" t="n">
-        <v>28619</v>
+        <v>243</v>
       </c>
       <c r="L10" t="n">
-        <v>37897</v>
+        <v>294</v>
       </c>
       <c r="M10" t="n">
-        <v>54472</v>
+        <v>726</v>
       </c>
       <c r="N10" t="n">
-        <v>81745</v>
+        <v>1788</v>
       </c>
       <c r="O10" t="n">
-        <v>109361</v>
+        <v>2657</v>
       </c>
       <c r="P10" t="n">
-        <v>141980</v>
+        <v>3405</v>
       </c>
       <c r="Q10" t="n">
-        <v>188324</v>
+        <v>5504</v>
       </c>
     </row>
     <row r="11">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Plug-in hybrid petrol-electric [ELC_PET_PI]</t>
+          <t>Alternative energy [ALT]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1072,40 +1072,40 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>385</v>
+        <v>5972</v>
       </c>
       <c r="G11" t="n">
-        <v>727</v>
+        <v>7931</v>
       </c>
       <c r="H11" t="n">
-        <v>1458</v>
+        <v>10125</v>
       </c>
       <c r="I11" t="n">
-        <v>2165</v>
+        <v>14459</v>
       </c>
       <c r="J11" t="n">
-        <v>3749</v>
+        <v>20180</v>
       </c>
       <c r="K11" t="n">
-        <v>5467</v>
+        <v>26732</v>
       </c>
       <c r="L11" t="n">
-        <v>7748</v>
+        <v>35642</v>
       </c>
       <c r="M11" t="n">
-        <v>14511</v>
+        <v>50615</v>
       </c>
       <c r="N11" t="n">
-        <v>27233</v>
+        <v>82381</v>
       </c>
       <c r="O11" t="n">
-        <v>38923</v>
+        <v>115799</v>
       </c>
       <c r="P11" t="n">
-        <v>53459</v>
+        <v>160671</v>
       </c>
       <c r="Q11" t="n">
-        <v>69264</v>
+        <v>205359</v>
       </c>
     </row>
     <row r="12">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Diesel (excluding hybrids) [DIE_X_HYB]</t>
+          <t>Electricity [ELC]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1133,40 +1133,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2621133</v>
+        <v>2070</v>
       </c>
       <c r="G12" t="n">
-        <v>2663063</v>
+        <v>3386</v>
       </c>
       <c r="H12" t="n">
-        <v>2702922</v>
+        <v>5032</v>
       </c>
       <c r="I12" t="n">
-        <v>2749046</v>
+        <v>9073</v>
       </c>
       <c r="J12" t="n">
-        <v>2770470</v>
+        <v>14618</v>
       </c>
       <c r="K12" t="n">
-        <v>2776332</v>
+        <v>20831</v>
       </c>
       <c r="L12" t="n">
-        <v>2772854</v>
+        <v>29523</v>
       </c>
       <c r="M12" t="n">
-        <v>2762273</v>
+        <v>44507</v>
       </c>
       <c r="N12" t="n">
-        <v>2717475</v>
+        <v>76539</v>
       </c>
       <c r="O12" t="n">
-        <v>2651280</v>
+        <v>110225</v>
       </c>
       <c r="P12" t="n">
-        <v>2584985</v>
+        <v>155490</v>
       </c>
       <c r="Q12" t="n">
-        <v>2510099</v>
+        <v>200603</v>
       </c>
     </row>
     <row r="13">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hybrid diesel-electric [ELC_DIE_HYB]</t>
+          <t>Hydrogen and fuel cells [HYD_FCELL]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1194,40 +1194,40 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>432</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>542</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>1028</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>1224</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
-        <v>1268</v>
+        <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>2220</v>
+        <v>24</v>
       </c>
       <c r="L13" t="n">
-        <v>5878</v>
+        <v>41</v>
       </c>
       <c r="M13" t="n">
-        <v>13652</v>
+        <v>45</v>
       </c>
       <c r="N13" t="n">
-        <v>26208</v>
+        <v>55</v>
       </c>
       <c r="O13" t="n">
-        <v>38745</v>
+        <v>62</v>
       </c>
       <c r="P13" t="n">
-        <v>52138</v>
+        <v>67</v>
       </c>
       <c r="Q13" t="n">
-        <v>66843</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Plug-in hybrid diesel-electric [ELC_DIE_PI]</t>
+          <t>Bioethanol [BIOETH]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1255,40 +1255,24 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
-      </c>
-      <c r="G14" t="n">
-        <v>49</v>
-      </c>
-      <c r="H14" t="n">
-        <v>49</v>
-      </c>
-      <c r="I14" t="n">
-        <v>113</v>
-      </c>
-      <c r="J14" t="n">
-        <v>187</v>
-      </c>
-      <c r="K14" t="n">
-        <v>243</v>
-      </c>
-      <c r="L14" t="n">
-        <v>294</v>
-      </c>
-      <c r="M14" t="n">
-        <v>726</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1788</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>2657</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3405</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1307,7 +1291,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hydrogen and fuel cells [HYD_FCELL]</t>
+          <t>Biodiesel [BIODIE]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1318,38 +1302,22 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>13</v>
-      </c>
-      <c r="J15" t="n">
-        <v>19</v>
-      </c>
-      <c r="K15" t="n">
-        <v>24</v>
-      </c>
-      <c r="L15" t="n">
-        <v>41</v>
-      </c>
-      <c r="M15" t="n">
-        <v>45</v>
-      </c>
-      <c r="N15" t="n">
-        <v>55</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1368,7 +1336,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bioethanol [BIOETH]</t>
+          <t>Natural gas [GAS]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1377,24 +1345,40 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+        <v>2219</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2397</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2475</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2457</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2433</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2365</v>
+      </c>
+      <c r="L16" t="n">
+        <v>2602</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2753</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2654</v>
+      </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2564</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2342</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1413,7 +1397,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Biodiesel [BIODIE]</t>
+          <t>Liquefied petroleum gases (LPG) [LPG]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1422,24 +1406,40 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+      <c r="L17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="18">
